--- a/reports/集团总公司_利润表_2026-03.xlsx
+++ b/reports/集团总公司_利润表_2026-03.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>201318580</v>
+        <v>221035420</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>147042631</v>
+        <v>161712066</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>449528077</v>
+        <v>489103159</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>699703</v>
+        <v>909807</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1933313</v>
+        <v>2509523</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>609139</v>
+        <v>795126</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1677383</v>
+        <v>2196074</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>515095</v>
+        <v>670161</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1421214</v>
+        <v>1853039</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>472692</v>
+        <v>617521</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1307646</v>
+        <v>1708918</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>257659</v>
+        <v>339053</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>710800</v>
+        <v>938647</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>206450</v>
+        <v>266821</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>568551</v>
+        <v>738577</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>198557842</v>
+        <v>217436931</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>144281893</v>
+        <v>158113577</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>62337385</v>
+        <v>70215035</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>215500307</v>
+        <v>237556220</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1597473</v>
+        <v>2831079</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>4406092</v>
+        <v>7800160</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1438455</v>
+        <v>2061339</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>3979568</v>
+        <v>5674792</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>77192779</v>
+        <v>81677533</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>213275146</v>
+        <v>224493423</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1655410</v>
+        <v>2069113</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4548818</v>
+        <v>5692417</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>720488</v>
+        <v>1034474</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1989560</v>
+        <v>2849260</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2563509</v>
+        <v>3104445</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>7107107</v>
+        <v>8559128</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1134605</v>
+        <v>1550127</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>3127571</v>
+        <v>4277919</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>54101422</v>
+        <v>53701733</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>148659342</v>
+        <v>148808118</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>174527</v>
+        <v>174877</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>512903</v>
+        <v>526110</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3269928</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>9051408</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2176816</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>6026215</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>163623525</v>
+        <v>184361961</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>131265574</v>
+        <v>137856676</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>103200910</v>
+        <v>109880575</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>284754193</v>
+        <v>303790897</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>28064664</v>
+        <v>27976101</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>77039840</v>
+        <v>76916243</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5454500</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>15025698</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1748521</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>4812834</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1094571</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3011845</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1314995</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3619123</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>986741</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2717618</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>657673</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1813273</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>547552</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1511564</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3037176</v>
+        <v>3040231</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>8384246</v>
+        <v>8407576</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1427594</v>
+        <v>1434085</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>3951457</v>
+        <v>3965648</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3715933</v>
+        <v>3692379</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>10237078</v>
+        <v>10220011</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>24094168</v>
+        <v>23894945</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>66231883</v>
+        <v>66086552</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>359848</v>
+        <v>2923910</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1031994</v>
+        <v>8068987</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1150826</v>
+        <v>1149267</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3375173</v>
+        <v>3451055</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1199022</v>
+        <v>1098891</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3485555</v>
+        <v>3298648</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>123721</v>
+        <v>123282</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>358357</v>
+        <v>369583</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>491019</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1469919</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>956441</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2632428</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>328432</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>982166</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>246587</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>737629</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>411147</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1230862</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1370034</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3777941</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>218983</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>657214</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>163990</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>492786</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>272837</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>820667</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>190665</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>573792</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>136010</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>409295</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>108730</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>327010</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>81548</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>245007</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>34934317</v>
+        <v>36439138</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>39827916</v>
+        <v>40615985</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>545706</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1502892</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>136665</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>408775</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>216605</v>
+        <v>216924</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>628971</v>
+        <v>648716</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>34717712</v>
+        <v>36767920</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7311639</v>
+        <v>7344240</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>21251600</v>
+        <v>21986083</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>27406073</v>
+        <v>29423680</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>27406073</v>
+        <v>29423680</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>27406073</v>
+        <v>29423680</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>27406073</v>
+        <v>29423680</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>27406073</v>
+        <v>29423680</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
